--- a/langchain-langgraph-bank/exports/langchain-langgraph-questions.xlsx
+++ b/langchain-langgraph-bank/exports/langchain-langgraph-questions.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Questions'!$A$1:$Q$321</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Questions'!$A$1:$R$321</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q321"/>
+  <dimension ref="A1:R321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -448,8 +448,9 @@
     <col width="55" customWidth="1" min="13" max="13"/>
     <col width="28" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="38" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="34" customWidth="1" min="16" max="16"/>
+    <col width="38" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -530,10 +531,15 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>Concepts</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>Source File</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Source Index</t>
         </is>
@@ -614,10 +620,15 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
+          <t>Agent, Utility &amp; Goal-Based Agents</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.1-batch01.json</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="n">
+      <c r="R2" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -696,10 +707,15 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.1-batch01.json</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="n">
+      <c r="R3" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -778,10 +794,15 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.1-batch01.json</t>
         </is>
       </c>
-      <c r="Q4" s="2" t="n">
+      <c r="R4" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -860,10 +881,15 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
+          <t>Agent, Tools &amp; Tool Discovery</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.1-batch01.json</t>
         </is>
       </c>
-      <c r="Q5" s="2" t="n">
+      <c r="R5" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -942,10 +968,15 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.1-batch01.json</t>
         </is>
       </c>
-      <c r="Q6" s="2" t="n">
+      <c r="R6" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1024,10 +1055,15 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
+          <t>Agent, Utility &amp; Goal-Based Agents, Guardrails, Human-in-the-Loop (HITL)</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.1-batch01.json</t>
         </is>
       </c>
-      <c r="Q7" s="2" t="n">
+      <c r="R7" s="2" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1106,10 +1142,15 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
+          <t>Agent, Utility &amp; Goal-Based Agents</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.1-batch01.json</t>
         </is>
       </c>
-      <c r="Q8" s="2" t="n">
+      <c r="R8" s="2" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1188,10 +1229,15 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
+          <t>Agent, Tools &amp; Tool Discovery</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.1-batch01.json</t>
         </is>
       </c>
-      <c r="Q9" s="2" t="n">
+      <c r="R9" s="2" t="n">
         <v>7</v>
       </c>
     </row>
@@ -1270,10 +1316,15 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
+          <t>Agent, Tools &amp; Tool Discovery, Evaluation &amp; Learning Loops</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.1-batch01.json</t>
         </is>
       </c>
-      <c r="Q10" s="2" t="n">
+      <c r="R10" s="2" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1352,10 +1403,15 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
+          <t>Agent, Tools &amp; Tool Discovery</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.1-batch01.json</t>
         </is>
       </c>
-      <c r="Q11" s="2" t="n">
+      <c r="R11" s="2" t="n">
         <v>9</v>
       </c>
     </row>
@@ -1433,10 +1489,15 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.1-batch02.json</t>
         </is>
       </c>
-      <c r="Q12" s="2" t="n">
+      <c r="R12" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1514,10 +1575,15 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
+          <t>Agent, Tools &amp; Tool Discovery, Evaluation &amp; Learning Loops</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.1-batch02.json</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="n">
+      <c r="R13" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1595,10 +1661,15 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
+          <t>Agent, Tools &amp; Tool Discovery</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.1-batch02.json</t>
         </is>
       </c>
-      <c r="Q14" s="2" t="n">
+      <c r="R14" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1676,10 +1747,15 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
+          <t>Agent, Utility &amp; Goal-Based Agents, Guardrails</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.1-batch02.json</t>
         </is>
       </c>
-      <c r="Q15" s="2" t="n">
+      <c r="R15" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1757,10 +1833,15 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
+          <t>Agent, Tools &amp; Tool Discovery, Utility &amp; Goal-Based Agents</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.1-batch02.json</t>
         </is>
       </c>
-      <c r="Q16" s="2" t="n">
+      <c r="R16" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1832,10 +1913,15 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.1-batch03.json</t>
         </is>
       </c>
-      <c r="Q17" s="2" t="n">
+      <c r="R17" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1908,10 +1994,15 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
+          <t>Agent, Tools &amp; Tool Discovery</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.1-batch03.json</t>
         </is>
       </c>
-      <c r="Q18" s="2" t="n">
+      <c r="R18" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1990,10 +2081,15 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.1-batch03.json</t>
         </is>
       </c>
-      <c r="Q19" s="2" t="n">
+      <c r="R19" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2075,10 +2171,15 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.1-batch03.json</t>
         </is>
       </c>
-      <c r="Q20" s="2" t="n">
+      <c r="R20" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2157,10 +2258,15 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
+          <t>Agent, Environment</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.1-batch04.json</t>
         </is>
       </c>
-      <c r="Q21" s="2" t="n">
+      <c r="R21" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2239,10 +2345,15 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
+          <t>Agent, Tools &amp; Tool Discovery</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.1-batch04.json</t>
         </is>
       </c>
-      <c r="Q22" s="2" t="n">
+      <c r="R22" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2321,10 +2432,15 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
+          <t>Agent, Utility &amp; Goal-Based Agents, Guardrails</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.1-batch04.json</t>
         </is>
       </c>
-      <c r="Q23" s="2" t="n">
+      <c r="R23" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2403,10 +2519,15 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
+          <t>Agent, Tools &amp; Tool Discovery, Utility &amp; Goal-Based Agents</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.1-batch04.json</t>
         </is>
       </c>
-      <c r="Q24" s="2" t="n">
+      <c r="R24" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2485,10 +2606,15 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
+          <t>Agent, Utility &amp; Goal-Based Agents</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.1-batch04.json</t>
         </is>
       </c>
-      <c r="Q25" s="2" t="n">
+      <c r="R25" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2567,10 +2693,15 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
+          <t>Agent, Tools &amp; Tool Discovery, Utility &amp; Goal-Based Agents</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.1-batch04.json</t>
         </is>
       </c>
-      <c r="Q26" s="2" t="n">
+      <c r="R26" s="2" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2649,10 +2780,15 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
+          <t>Agent, Environment, Perception, Reasoning Loop (ReAct)</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.2-batch01.json</t>
         </is>
       </c>
-      <c r="Q27" s="2" t="n">
+      <c r="R27" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2731,10 +2867,15 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
+          <t>Agent, Perception, Reasoning Loop (ReAct), Error Recovery</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.2-batch01.json</t>
         </is>
       </c>
-      <c r="Q28" s="2" t="n">
+      <c r="R28" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2813,10 +2954,15 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
+          <t>Agent, Reasoning Loop (ReAct)</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.2-batch01.json</t>
         </is>
       </c>
-      <c r="Q29" s="2" t="n">
+      <c r="R29" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2895,10 +3041,15 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
+          <t>Agent, Reasoning Loop (ReAct), Guardrails</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.2-batch01.json</t>
         </is>
       </c>
-      <c r="Q30" s="2" t="n">
+      <c r="R30" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2977,10 +3128,15 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
+          <t>Agent, State / State Management, Reasoning Loop (ReAct)</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.2-batch01.json</t>
         </is>
       </c>
-      <c r="Q31" s="2" t="n">
+      <c r="R31" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -3059,10 +3215,15 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
+          <t>Agent, Perception, Reasoning Loop (ReAct), Error Recovery</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.2-batch01.json</t>
         </is>
       </c>
-      <c r="Q32" s="2" t="n">
+      <c r="R32" s="2" t="n">
         <v>5</v>
       </c>
     </row>
@@ -3141,10 +3302,15 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
+          <t>Agent, Perception, State / State Management, Reasoning Loop (ReAct)</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.2-batch01.json</t>
         </is>
       </c>
-      <c r="Q33" s="2" t="n">
+      <c r="R33" s="2" t="n">
         <v>6</v>
       </c>
     </row>
@@ -3223,10 +3389,15 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
+          <t>Agent, Reasoning Loop (ReAct)</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.2-batch01.json</t>
         </is>
       </c>
-      <c r="Q34" s="2" t="n">
+      <c r="R34" s="2" t="n">
         <v>7</v>
       </c>
     </row>
@@ -3305,10 +3476,15 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
+          <t>Agent, Perception, Reasoning Loop (ReAct), Error Recovery</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.2-batch01.json</t>
         </is>
       </c>
-      <c r="Q35" s="2" t="n">
+      <c r="R35" s="2" t="n">
         <v>8</v>
       </c>
     </row>
@@ -3387,10 +3563,15 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
+          <t>Agent, Reasoning Loop (ReAct)</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.2-batch01.json</t>
         </is>
       </c>
-      <c r="Q36" s="2" t="n">
+      <c r="R36" s="2" t="n">
         <v>9</v>
       </c>
     </row>
@@ -3468,10 +3649,15 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
+          <t>Agent, Reasoning Loop (ReAct)</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.2-batch02.json</t>
         </is>
       </c>
-      <c r="Q37" s="2" t="n">
+      <c r="R37" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3549,10 +3735,15 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
+          <t>Agent, Perception, Reasoning Loop (ReAct), Error Recovery</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.2-batch02.json</t>
         </is>
       </c>
-      <c r="Q38" s="2" t="n">
+      <c r="R38" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3630,10 +3821,15 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
+          <t>Agent, Reasoning Loop (ReAct)</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.2-batch02.json</t>
         </is>
       </c>
-      <c r="Q39" s="2" t="n">
+      <c r="R39" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3711,10 +3907,15 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
+          <t>Agent, State / State Management, Reasoning Loop (ReAct)</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.2-batch02.json</t>
         </is>
       </c>
-      <c r="Q40" s="2" t="n">
+      <c r="R40" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3792,10 +3993,15 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
+          <t>Agent, Perception, Reasoning Loop (ReAct)</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.2-batch02.json</t>
         </is>
       </c>
-      <c r="Q41" s="2" t="n">
+      <c r="R41" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -3867,10 +4073,15 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
+          <t>Agent, Perception, State / State Management, Reasoning Loop (ReAct)</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.2-batch03.json</t>
         </is>
       </c>
-      <c r="Q42" s="2" t="n">
+      <c r="R42" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3943,10 +4154,15 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
+          <t>Agent, State / State Management, Reasoning Loop (ReAct)</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.2-batch03.json</t>
         </is>
       </c>
-      <c r="Q43" s="2" t="n">
+      <c r="R43" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4025,10 +4241,15 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
+          <t>Agent, Perception, Reasoning Loop (ReAct), Error Recovery</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.2-batch03.json</t>
         </is>
       </c>
-      <c r="Q44" s="2" t="n">
+      <c r="R44" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4110,10 +4331,15 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
+          <t>Agent, Reasoning Loop (ReAct), Guardrails</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.2-batch03.json</t>
         </is>
       </c>
-      <c r="Q45" s="2" t="n">
+      <c r="R45" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4192,10 +4418,15 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
+          <t>Agent, Reasoning Loop (ReAct)</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.2-batch04.json</t>
         </is>
       </c>
-      <c r="Q46" s="2" t="n">
+      <c r="R46" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4274,10 +4505,15 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
+          <t>Agent, Perception, Reasoning Loop (ReAct)</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.2-batch04.json</t>
         </is>
       </c>
-      <c r="Q47" s="2" t="n">
+      <c r="R47" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4356,10 +4592,15 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
+          <t>Agent, State / State Management, Reasoning Loop (ReAct)</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.2-batch04.json</t>
         </is>
       </c>
-      <c r="Q48" s="2" t="n">
+      <c r="R48" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4438,10 +4679,15 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
+          <t>Agent, Perception, State / State Management, Reasoning Loop (ReAct)</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.2-batch04.json</t>
         </is>
       </c>
-      <c r="Q49" s="2" t="n">
+      <c r="R49" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4520,10 +4766,15 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
+          <t>Agent, Perception, Reasoning Loop (ReAct), Error Recovery</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.2-batch04.json</t>
         </is>
       </c>
-      <c r="Q50" s="2" t="n">
+      <c r="R50" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4602,10 +4853,15 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
+          <t>Agent, Reflex Agents</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.3-batch01.json</t>
         </is>
       </c>
-      <c r="Q51" s="2" t="n">
+      <c r="R51" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4684,10 +4940,15 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
+          <t>Agent, Planning</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.3-batch01.json</t>
         </is>
       </c>
-      <c r="Q52" s="2" t="n">
+      <c r="R52" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4766,10 +5027,15 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
+          <t>Agent, Environment</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.3-batch01.json</t>
         </is>
       </c>
-      <c r="Q53" s="2" t="n">
+      <c r="R53" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4848,10 +5114,15 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
+          <t>Agent, Environment, Planning, Reflex Agents</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.3-batch01.json</t>
         </is>
       </c>
-      <c r="Q54" s="2" t="n">
+      <c r="R54" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4930,10 +5201,15 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.3-batch01.json</t>
         </is>
       </c>
-      <c r="Q55" s="2" t="n">
+      <c r="R55" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5012,10 +5288,15 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
+          <t>Agent, Reflex Agents</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.3-batch01.json</t>
         </is>
       </c>
-      <c r="Q56" s="2" t="n">
+      <c r="R56" s="2" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5093,10 +5374,15 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
+          <t>Agent, Planning</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.3-batch02.json</t>
         </is>
       </c>
-      <c r="Q57" s="2" t="n">
+      <c r="R57" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5174,10 +5460,15 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
+          <t>Agent, Environment, Planning</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.3-batch02.json</t>
         </is>
       </c>
-      <c r="Q58" s="2" t="n">
+      <c r="R58" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5255,10 +5546,15 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
+          <t>Agent, Environment</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.3-batch02.json</t>
         </is>
       </c>
-      <c r="Q59" s="2" t="n">
+      <c r="R59" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5336,10 +5632,15 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
+          <t>Agent, Reflex Agents</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.3-batch02.json</t>
         </is>
       </c>
-      <c r="Q60" s="2" t="n">
+      <c r="R60" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5411,10 +5712,15 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
+          <t>Agent, Environment</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.3-batch03.json</t>
         </is>
       </c>
-      <c r="Q61" s="2" t="n">
+      <c r="R61" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5486,10 +5792,15 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
+          <t>Agent, Environment, Planning</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.3-batch03.json</t>
         </is>
       </c>
-      <c r="Q62" s="2" t="n">
+      <c r="R62" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5568,10 +5879,15 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
+          <t>Agent, Environment</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.3-batch03.json</t>
         </is>
       </c>
-      <c r="Q63" s="2" t="n">
+      <c r="R63" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5650,10 +5966,15 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
+          <t>Agent, Environment, Planning</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.3-batch03.json</t>
         </is>
       </c>
-      <c r="Q64" s="2" t="n">
+      <c r="R64" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5732,10 +6053,15 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
+          <t>Agent, Planning</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.3-batch04.json</t>
         </is>
       </c>
-      <c r="Q65" s="2" t="n">
+      <c r="R65" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5814,10 +6140,15 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
+          <t>Agent, Environment, Planning</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.3-batch04.json</t>
         </is>
       </c>
-      <c r="Q66" s="2" t="n">
+      <c r="R66" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5896,10 +6227,15 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
+          <t>Agent, Environment</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.3-batch04.json</t>
         </is>
       </c>
-      <c r="Q67" s="2" t="n">
+      <c r="R67" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5978,10 +6314,15 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
+          <t>Agent, Environment, Planning</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.3-batch04.json</t>
         </is>
       </c>
-      <c r="Q68" s="2" t="n">
+      <c r="R68" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6060,10 +6401,15 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
+          <t>Agent, Reflex Agents</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.3-batch05.json</t>
         </is>
       </c>
-      <c r="Q69" s="2" t="n">
+      <c r="R69" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6142,10 +6488,15 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
+          <t>Agent, Planning</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.3-batch05.json</t>
         </is>
       </c>
-      <c r="Q70" s="2" t="n">
+      <c r="R70" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6223,10 +6574,15 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
+          <t>Agent, Environment</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.3-batch05.json</t>
         </is>
       </c>
-      <c r="Q71" s="2" t="n">
+      <c r="R71" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6305,10 +6661,15 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
+          <t>Agent, Environment, Planning</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.3-batch05.json</t>
         </is>
       </c>
-      <c r="Q72" s="2" t="n">
+      <c r="R72" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6387,10 +6748,15 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
+          <t>Agent, Environment, Planning</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d1\1.3-batch05.json</t>
         </is>
       </c>
-      <c r="Q73" s="2" t="n">
+      <c r="R73" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -6469,10 +6835,15 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
+          <t>Reasoning Loop (ReAct)</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.1-batch01.json</t>
         </is>
       </c>
-      <c r="Q74" s="2" t="n">
+      <c r="R74" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6551,10 +6922,15 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery, Reasoning Loop (ReAct), Error Recovery</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.1-batch01.json</t>
         </is>
       </c>
-      <c r="Q75" s="2" t="n">
+      <c r="R75" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6633,10 +7009,15 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
+          <t>Reasoning Loop (ReAct)</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.1-batch01.json</t>
         </is>
       </c>
-      <c r="Q76" s="2" t="n">
+      <c r="R76" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -6715,10 +7096,15 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
+          <t>Reasoning Loop (ReAct), Error Recovery</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.1-batch01.json</t>
         </is>
       </c>
-      <c r="Q77" s="2" t="n">
+      <c r="R77" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6797,10 +7183,15 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
+          <t>Reasoning Loop (ReAct), Chain of Thought (CoT)</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.1-batch01.json</t>
         </is>
       </c>
-      <c r="Q78" s="2" t="n">
+      <c r="R78" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -6879,10 +7270,15 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
+          <t>Reasoning Loop (ReAct), Error Recovery</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.1-batch01.json</t>
         </is>
       </c>
-      <c r="Q79" s="2" t="n">
+      <c r="R79" s="2" t="n">
         <v>5</v>
       </c>
     </row>
@@ -6960,10 +7356,15 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery, Reasoning Loop (ReAct), Chain of Thought (CoT)</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.1-batch02.json</t>
         </is>
       </c>
-      <c r="Q80" s="2" t="n">
+      <c r="R80" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7040,10 +7441,15 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
+          <t>Reasoning Loop (ReAct), Error Recovery</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.1-batch02.json</t>
         </is>
       </c>
-      <c r="Q81" s="2" t="n">
+      <c r="R81" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7115,10 +7521,15 @@
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
+          <t>Reasoning Loop (ReAct)</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.1-batch02.json</t>
         </is>
       </c>
-      <c r="Q82" s="2" t="n">
+      <c r="R82" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -7190,10 +7601,15 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery, Reasoning Loop (ReAct), Error Recovery</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.1-batch02.json</t>
         </is>
       </c>
-      <c r="Q83" s="2" t="n">
+      <c r="R83" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7272,10 +7688,15 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
+          <t>Reasoning Loop (ReAct), Error Recovery</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.1-batch02.json</t>
         </is>
       </c>
-      <c r="Q84" s="2" t="n">
+      <c r="R84" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7354,10 +7775,15 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
+          <t>Reasoning Loop (ReAct)</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.1-batch03.json</t>
         </is>
       </c>
-      <c r="Q85" s="2" t="n">
+      <c r="R85" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7436,10 +7862,15 @@
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery, Reasoning Loop (ReAct)</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.1-batch03.json</t>
         </is>
       </c>
-      <c r="Q86" s="2" t="n">
+      <c r="R86" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7518,10 +7949,15 @@
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
+          <t>Reasoning Loop (ReAct)</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.1-batch03.json</t>
         </is>
       </c>
-      <c r="Q87" s="2" t="n">
+      <c r="R87" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -7600,10 +8036,15 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
+          <t>Reasoning Loop (ReAct)</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.1-batch03.json</t>
         </is>
       </c>
-      <c r="Q88" s="2" t="n">
+      <c r="R88" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -7682,10 +8123,15 @@
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
+          <t>Reasoning Loop (ReAct), Error Recovery</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.1-batch03.json</t>
         </is>
       </c>
-      <c r="Q89" s="2" t="n">
+      <c r="R89" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7764,10 +8210,15 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
+          <t>Reasoning Loop (ReAct), Chain of Thought (CoT)</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.1-batch04.json</t>
         </is>
       </c>
-      <c r="Q90" s="2" t="n">
+      <c r="R90" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7845,10 +8296,15 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
+          <t>Reasoning Loop (ReAct)</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.1-batch04.json</t>
         </is>
       </c>
-      <c r="Q91" s="2" t="n">
+      <c r="R91" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -7927,10 +8383,15 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
+          <t>Reasoning Loop (ReAct), Error Recovery</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.1-batch04.json</t>
         </is>
       </c>
-      <c r="Q92" s="2" t="n">
+      <c r="R92" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -8009,10 +8470,15 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery, Reasoning Loop (ReAct)</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.1-batch04.json</t>
         </is>
       </c>
-      <c r="Q93" s="2" t="n">
+      <c r="R93" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8091,10 +8557,15 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
+          <t>Reasoning Loop (ReAct), Chain of Thought (CoT)</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.1-batch04.json</t>
         </is>
       </c>
-      <c r="Q94" s="2" t="n">
+      <c r="R94" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -8173,10 +8644,15 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
+          <t>Planning</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.2-batch01.json</t>
         </is>
       </c>
-      <c r="Q95" s="2" t="n">
+      <c r="R95" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8255,10 +8731,15 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
+          <t>State / State Management, Planning</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.2-batch01.json</t>
         </is>
       </c>
-      <c r="Q96" s="2" t="n">
+      <c r="R96" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8337,10 +8818,15 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
+          <t>Chain of Thought (CoT), Planning</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.2-batch01.json</t>
         </is>
       </c>
-      <c r="Q97" s="2" t="n">
+      <c r="R97" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -8419,10 +8905,15 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
+          <t>Planning</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.2-batch01.json</t>
         </is>
       </c>
-      <c r="Q98" s="2" t="n">
+      <c r="R98" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8501,10 +8992,15 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
+          <t>State / State Management, Planning</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.2-batch02.json</t>
         </is>
       </c>
-      <c r="Q99" s="2" t="n">
+      <c r="R99" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8583,10 +9079,15 @@
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
+          <t>Chain of Thought (CoT), Planning</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.2-batch02.json</t>
         </is>
       </c>
-      <c r="Q100" s="2" t="n">
+      <c r="R100" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8664,10 +9165,15 @@
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
+          <t>Planning</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.2-batch02.json</t>
         </is>
       </c>
-      <c r="Q101" s="2" t="n">
+      <c r="R101" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -8744,10 +9250,15 @@
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
+          <t>Planning</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.2-batch02.json</t>
         </is>
       </c>
-      <c r="Q102" s="2" t="n">
+      <c r="R102" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -8819,10 +9330,15 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
+          <t>State / State Management, Planning</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.2-batch03.json</t>
         </is>
       </c>
-      <c r="Q103" s="2" t="n">
+      <c r="R103" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8894,10 +9410,15 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
+          <t>State / State Management, Chain of Thought (CoT), Planning</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.2-batch03.json</t>
         </is>
       </c>
-      <c r="Q104" s="2" t="n">
+      <c r="R104" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -8976,10 +9497,15 @@
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
+          <t>Planning</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.2-batch03.json</t>
         </is>
       </c>
-      <c r="Q105" s="2" t="n">
+      <c r="R105" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -9058,10 +9584,15 @@
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
+          <t>Planning</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.2-batch04.json</t>
         </is>
       </c>
-      <c r="Q106" s="2" t="n">
+      <c r="R106" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9140,10 +9671,15 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
+          <t>Planning</t>
+        </is>
+      </c>
+      <c r="Q107" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.2-batch04.json</t>
         </is>
       </c>
-      <c r="Q107" s="2" t="n">
+      <c r="R107" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9222,10 +9758,15 @@
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
+          <t>Chain of Thought (CoT), Planning</t>
+        </is>
+      </c>
+      <c r="Q108" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.2-batch04.json</t>
         </is>
       </c>
-      <c r="Q108" s="2" t="n">
+      <c r="R108" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -9304,10 +9845,15 @@
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
+          <t>State / State Management, Planning</t>
+        </is>
+      </c>
+      <c r="Q109" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.2-batch05.json</t>
         </is>
       </c>
-      <c r="Q109" s="2" t="n">
+      <c r="R109" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9386,10 +9932,15 @@
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
+          <t>Planning</t>
+        </is>
+      </c>
+      <c r="Q110" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.2-batch05.json</t>
         </is>
       </c>
-      <c r="Q110" s="2" t="n">
+      <c r="R110" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9467,10 +10018,15 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
+          <t>Planning</t>
+        </is>
+      </c>
+      <c r="Q111" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.2-batch05.json</t>
         </is>
       </c>
-      <c r="Q111" s="2" t="n">
+      <c r="R111" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -9549,10 +10105,15 @@
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
+          <t>Planning, Error Recovery</t>
+        </is>
+      </c>
+      <c r="Q112" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.2-batch06.json</t>
         </is>
       </c>
-      <c r="Q112" s="2" t="n">
+      <c r="R112" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9631,10 +10192,15 @@
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
+          <t>Chain of Thought (CoT), Planning</t>
+        </is>
+      </c>
+      <c r="Q113" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.2-batch06.json</t>
         </is>
       </c>
-      <c r="Q113" s="2" t="n">
+      <c r="R113" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -9713,10 +10279,15 @@
       </c>
       <c r="P114" s="2" t="inlineStr">
         <is>
+          <t>State / State Management, Planning</t>
+        </is>
+      </c>
+      <c r="Q114" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.2-batch06.json</t>
         </is>
       </c>
-      <c r="Q114" s="2" t="n">
+      <c r="R114" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -9794,10 +10365,15 @@
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
+          <t>Planning</t>
+        </is>
+      </c>
+      <c r="Q115" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.2-batch06.json</t>
         </is>
       </c>
-      <c r="Q115" s="2" t="n">
+      <c r="R115" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -9876,10 +10452,15 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
+          <t>Planning</t>
+        </is>
+      </c>
+      <c r="Q116" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.2-batch06.json</t>
         </is>
       </c>
-      <c r="Q116" s="2" t="n">
+      <c r="R116" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -9958,10 +10539,15 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
+          <t>Context Engineering, Evaluation &amp; Learning Loops</t>
+        </is>
+      </c>
+      <c r="Q117" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.3-batch01.json</t>
         </is>
       </c>
-      <c r="Q117" s="2" t="n">
+      <c r="R117" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10040,10 +10626,15 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
+          <t>Context Engineering, Evaluation &amp; Learning Loops</t>
+        </is>
+      </c>
+      <c r="Q118" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.3-batch01.json</t>
         </is>
       </c>
-      <c r="Q118" s="2" t="n">
+      <c r="R118" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10122,10 +10713,15 @@
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
+          <t>Evaluation &amp; Learning Loops</t>
+        </is>
+      </c>
+      <c r="Q119" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.3-batch01.json</t>
         </is>
       </c>
-      <c r="Q119" s="2" t="n">
+      <c r="R119" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -10204,10 +10800,15 @@
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
+          <t>Context Engineering, Evaluation &amp; Learning Loops</t>
+        </is>
+      </c>
+      <c r="Q120" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.3-batch02.json</t>
         </is>
       </c>
-      <c r="Q120" s="2" t="n">
+      <c r="R120" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10286,10 +10887,15 @@
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
+          <t>Context Engineering, Evaluation &amp; Learning Loops</t>
+        </is>
+      </c>
+      <c r="Q121" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.3-batch02.json</t>
         </is>
       </c>
-      <c r="Q121" s="2" t="n">
+      <c r="R121" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10368,10 +10974,15 @@
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
+          <t>Context Engineering, Evaluation &amp; Learning Loops</t>
+        </is>
+      </c>
+      <c r="Q122" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.3-batch02.json</t>
         </is>
       </c>
-      <c r="Q122" s="2" t="n">
+      <c r="R122" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -10449,10 +11060,15 @@
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
+          <t>Context Engineering, Evaluation &amp; Learning Loops</t>
+        </is>
+      </c>
+      <c r="Q123" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.3-batch03.json</t>
         </is>
       </c>
-      <c r="Q123" s="2" t="n">
+      <c r="R123" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10524,10 +11140,15 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
+          <t>Context Engineering, Evaluation &amp; Learning Loops</t>
+        </is>
+      </c>
+      <c r="Q124" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.3-batch03.json</t>
         </is>
       </c>
-      <c r="Q124" s="2" t="n">
+      <c r="R124" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10606,10 +11227,15 @@
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
+          <t>Context Engineering, Evaluation &amp; Learning Loops</t>
+        </is>
+      </c>
+      <c r="Q125" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.3-batch03.json</t>
         </is>
       </c>
-      <c r="Q125" s="2" t="n">
+      <c r="R125" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -10688,10 +11314,15 @@
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
+          <t>Context Engineering, Evaluation &amp; Learning Loops</t>
+        </is>
+      </c>
+      <c r="Q126" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.3-batch04.json</t>
         </is>
       </c>
-      <c r="Q126" s="2" t="n">
+      <c r="R126" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10770,10 +11401,15 @@
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
+          <t>Guardrails, Evaluation &amp; Learning Loops</t>
+        </is>
+      </c>
+      <c r="Q127" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.3-batch04.json</t>
         </is>
       </c>
-      <c r="Q127" s="2" t="n">
+      <c r="R127" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -10852,10 +11488,15 @@
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
+          <t>Context Engineering, Evaluation &amp; Learning Loops</t>
+        </is>
+      </c>
+      <c r="Q128" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.3-batch04.json</t>
         </is>
       </c>
-      <c r="Q128" s="2" t="n">
+      <c r="R128" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -10933,10 +11574,15 @@
       </c>
       <c r="P129" s="2" t="inlineStr">
         <is>
+          <t>Context Engineering, Evaluation &amp; Learning Loops</t>
+        </is>
+      </c>
+      <c r="Q129" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.3-batch05.json</t>
         </is>
       </c>
-      <c r="Q129" s="2" t="n">
+      <c r="R129" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11015,10 +11661,15 @@
       </c>
       <c r="P130" s="2" t="inlineStr">
         <is>
+          <t>Context Engineering, Evaluation &amp; Learning Loops</t>
+        </is>
+      </c>
+      <c r="Q130" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.3-batch05.json</t>
         </is>
       </c>
-      <c r="Q130" s="2" t="n">
+      <c r="R130" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11097,10 +11748,15 @@
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
+          <t>Context Engineering, Evaluation &amp; Learning Loops</t>
+        </is>
+      </c>
+      <c r="Q131" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.3-batch05.json</t>
         </is>
       </c>
-      <c r="Q131" s="2" t="n">
+      <c r="R131" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -11179,10 +11835,15 @@
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
+          <t>Context Engineering, Evaluation &amp; Learning Loops</t>
+        </is>
+      </c>
+      <c r="Q132" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.3-batch06.json</t>
         </is>
       </c>
-      <c r="Q132" s="2" t="n">
+      <c r="R132" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11261,10 +11922,15 @@
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
+          <t>Context Engineering, Evaluation &amp; Learning Loops</t>
+        </is>
+      </c>
+      <c r="Q133" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.3-batch06.json</t>
         </is>
       </c>
-      <c r="Q133" s="2" t="n">
+      <c r="R133" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11343,10 +12009,15 @@
       </c>
       <c r="P134" s="2" t="inlineStr">
         <is>
+          <t>Evaluation &amp; Learning Loops</t>
+        </is>
+      </c>
+      <c r="Q134" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.3-batch06.json</t>
         </is>
       </c>
-      <c r="Q134" s="2" t="n">
+      <c r="R134" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -11425,10 +12096,15 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
+          <t>Context Engineering, Evaluation &amp; Learning Loops</t>
+        </is>
+      </c>
+      <c r="Q135" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.3-batch06.json</t>
         </is>
       </c>
-      <c r="Q135" s="2" t="n">
+      <c r="R135" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -11506,10 +12182,15 @@
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
+          <t>Context Engineering, Evaluation &amp; Learning Loops</t>
+        </is>
+      </c>
+      <c r="Q136" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.3-batch06.json</t>
         </is>
       </c>
-      <c r="Q136" s="2" t="n">
+      <c r="R136" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -11588,10 +12269,15 @@
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
+          <t>Context Engineering, Evaluation &amp; Learning Loops</t>
+        </is>
+      </c>
+      <c r="Q137" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.3-batch07.json</t>
         </is>
       </c>
-      <c r="Q137" s="2" t="n">
+      <c r="R137" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11670,10 +12356,15 @@
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
+          <t>Context Engineering, Evaluation &amp; Learning Loops</t>
+        </is>
+      </c>
+      <c r="Q138" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.3-batch07.json</t>
         </is>
       </c>
-      <c r="Q138" s="2" t="n">
+      <c r="R138" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11752,10 +12443,15 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
+          <t>Context Engineering, Error Recovery</t>
+        </is>
+      </c>
+      <c r="Q139" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.4-batch01.json</t>
         </is>
       </c>
-      <c r="Q139" s="2" t="n">
+      <c r="R139" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11834,10 +12530,15 @@
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
+          <t>Context Engineering, Error Recovery</t>
+        </is>
+      </c>
+      <c r="Q140" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.4-batch01.json</t>
         </is>
       </c>
-      <c r="Q140" s="2" t="n">
+      <c r="R140" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11916,10 +12617,15 @@
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
+          <t>Planning, Error Recovery</t>
+        </is>
+      </c>
+      <c r="Q141" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.4-batch01.json</t>
         </is>
       </c>
-      <c r="Q141" s="2" t="n">
+      <c r="R141" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -11998,10 +12704,15 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
+          <t>Context Engineering, Error Recovery</t>
+        </is>
+      </c>
+      <c r="Q142" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.4-batch02.json</t>
         </is>
       </c>
-      <c r="Q142" s="2" t="n">
+      <c r="R142" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12080,10 +12791,15 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
+          <t>Context Engineering, Error Recovery</t>
+        </is>
+      </c>
+      <c r="Q143" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.4-batch02.json</t>
         </is>
       </c>
-      <c r="Q143" s="2" t="n">
+      <c r="R143" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12162,10 +12878,15 @@
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
+          <t>Error Recovery</t>
+        </is>
+      </c>
+      <c r="Q144" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.4-batch02.json</t>
         </is>
       </c>
-      <c r="Q144" s="2" t="n">
+      <c r="R144" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -12242,10 +12963,15 @@
       </c>
       <c r="P145" s="2" t="inlineStr">
         <is>
+          <t>Error Recovery</t>
+        </is>
+      </c>
+      <c r="Q145" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.4-batch03.json</t>
         </is>
       </c>
-      <c r="Q145" s="2" t="n">
+      <c r="R145" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12317,10 +13043,15 @@
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
+          <t>Planning, Error Recovery</t>
+        </is>
+      </c>
+      <c r="Q146" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.4-batch03.json</t>
         </is>
       </c>
-      <c r="Q146" s="2" t="n">
+      <c r="R146" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12399,10 +13130,15 @@
       </c>
       <c r="P147" s="2" t="inlineStr">
         <is>
+          <t>Context Engineering, Error Recovery</t>
+        </is>
+      </c>
+      <c r="Q147" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.4-batch03.json</t>
         </is>
       </c>
-      <c r="Q147" s="2" t="n">
+      <c r="R147" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -12481,10 +13217,15 @@
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
+          <t>Context Engineering, Error Recovery</t>
+        </is>
+      </c>
+      <c r="Q148" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.4-batch04.json</t>
         </is>
       </c>
-      <c r="Q148" s="2" t="n">
+      <c r="R148" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12563,10 +13304,15 @@
       </c>
       <c r="P149" s="2" t="inlineStr">
         <is>
+          <t>Context Engineering, Error Recovery</t>
+        </is>
+      </c>
+      <c r="Q149" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.4-batch04.json</t>
         </is>
       </c>
-      <c r="Q149" s="2" t="n">
+      <c r="R149" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12645,10 +13391,15 @@
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
+          <t>Context Engineering, Error Recovery, Evaluation &amp; Learning Loops</t>
+        </is>
+      </c>
+      <c r="Q150" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.4-batch04.json</t>
         </is>
       </c>
-      <c r="Q150" s="2" t="n">
+      <c r="R150" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -12727,10 +13478,15 @@
       </c>
       <c r="P151" s="2" t="inlineStr">
         <is>
+          <t>Context Engineering, Error Recovery</t>
+        </is>
+      </c>
+      <c r="Q151" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.4-batch05.json</t>
         </is>
       </c>
-      <c r="Q151" s="2" t="n">
+      <c r="R151" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12809,10 +13565,15 @@
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
+          <t>Error Recovery, Evaluation &amp; Learning Loops</t>
+        </is>
+      </c>
+      <c r="Q152" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.4-batch05.json</t>
         </is>
       </c>
-      <c r="Q152" s="2" t="n">
+      <c r="R152" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -12890,10 +13651,15 @@
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
+          <t>Context Engineering, Error Recovery</t>
+        </is>
+      </c>
+      <c r="Q153" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.4-batch05.json</t>
         </is>
       </c>
-      <c r="Q153" s="2" t="n">
+      <c r="R153" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -12972,10 +13738,15 @@
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
+          <t>Error Recovery</t>
+        </is>
+      </c>
+      <c r="Q154" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.4-batch06.json</t>
         </is>
       </c>
-      <c r="Q154" s="2" t="n">
+      <c r="R154" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13054,10 +13825,15 @@
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
+          <t>Context Engineering, Error Recovery</t>
+        </is>
+      </c>
+      <c r="Q155" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.4-batch06.json</t>
         </is>
       </c>
-      <c r="Q155" s="2" t="n">
+      <c r="R155" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13136,10 +13912,15 @@
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
+          <t>Error Recovery</t>
+        </is>
+      </c>
+      <c r="Q156" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.4-batch06.json</t>
         </is>
       </c>
-      <c r="Q156" s="2" t="n">
+      <c r="R156" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -13218,10 +13999,15 @@
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
+          <t>Context Engineering, Error Recovery</t>
+        </is>
+      </c>
+      <c r="Q157" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.4-batch06.json</t>
         </is>
       </c>
-      <c r="Q157" s="2" t="n">
+      <c r="R157" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -13300,10 +14086,15 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
+          <t>Context Engineering, Error Recovery</t>
+        </is>
+      </c>
+      <c r="Q158" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.4-batch06.json</t>
         </is>
       </c>
-      <c r="Q158" s="2" t="n">
+      <c r="R158" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -13381,10 +14172,15 @@
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
+          <t>Context Engineering, Error Recovery</t>
+        </is>
+      </c>
+      <c r="Q159" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d2\2.4-batch06.json</t>
         </is>
       </c>
-      <c r="Q159" s="2" t="n">
+      <c r="R159" s="2" t="n">
         <v>5</v>
       </c>
     </row>
@@ -13463,10 +14259,15 @@
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
+          <t>Environment, Tools &amp; Tool Discovery</t>
+        </is>
+      </c>
+      <c r="Q160" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.1-batch01.json</t>
         </is>
       </c>
-      <c r="Q160" s="2" t="n">
+      <c r="R160" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13545,10 +14346,15 @@
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
+          <t>Environment, Tools &amp; Tool Discovery</t>
+        </is>
+      </c>
+      <c r="Q161" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.1-batch01.json</t>
         </is>
       </c>
-      <c r="Q161" s="2" t="n">
+      <c r="R161" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13627,10 +14433,15 @@
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery, Guardrails</t>
+        </is>
+      </c>
+      <c r="Q162" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.1-batch01.json</t>
         </is>
       </c>
-      <c r="Q162" s="2" t="n">
+      <c r="R162" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -13709,10 +14520,15 @@
       </c>
       <c r="P163" s="2" t="inlineStr">
         <is>
+          <t>Environment, Tools &amp; Tool Discovery</t>
+        </is>
+      </c>
+      <c r="Q163" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.1-batch02.json</t>
         </is>
       </c>
-      <c r="Q163" s="2" t="n">
+      <c r="R163" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13791,10 +14607,15 @@
       </c>
       <c r="P164" s="2" t="inlineStr">
         <is>
+          <t>Environment, Tools &amp; Tool Discovery</t>
+        </is>
+      </c>
+      <c r="Q164" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.1-batch02.json</t>
         </is>
       </c>
-      <c r="Q164" s="2" t="n">
+      <c r="R164" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -13873,10 +14694,15 @@
       </c>
       <c r="P165" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery</t>
+        </is>
+      </c>
+      <c r="Q165" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.1-batch02.json</t>
         </is>
       </c>
-      <c r="Q165" s="2" t="n">
+      <c r="R165" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -13953,10 +14779,15 @@
       </c>
       <c r="P166" s="2" t="inlineStr">
         <is>
+          <t>Environment, Tools &amp; Tool Discovery</t>
+        </is>
+      </c>
+      <c r="Q166" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.1-batch03.json</t>
         </is>
       </c>
-      <c r="Q166" s="2" t="n">
+      <c r="R166" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14028,10 +14859,15 @@
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery</t>
+        </is>
+      </c>
+      <c r="Q167" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.1-batch03.json</t>
         </is>
       </c>
-      <c r="Q167" s="2" t="n">
+      <c r="R167" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14110,10 +14946,15 @@
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
+          <t>Environment, Tools &amp; Tool Discovery</t>
+        </is>
+      </c>
+      <c r="Q168" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.1-batch03.json</t>
         </is>
       </c>
-      <c r="Q168" s="2" t="n">
+      <c r="R168" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -14192,10 +15033,15 @@
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
+          <t>Environment, Tools &amp; Tool Discovery</t>
+        </is>
+      </c>
+      <c r="Q169" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.1-batch04.json</t>
         </is>
       </c>
-      <c r="Q169" s="2" t="n">
+      <c r="R169" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14274,10 +15120,15 @@
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery, Guardrails</t>
+        </is>
+      </c>
+      <c r="Q170" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.1-batch04.json</t>
         </is>
       </c>
-      <c r="Q170" s="2" t="n">
+      <c r="R170" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14356,10 +15207,15 @@
       </c>
       <c r="P171" s="2" t="inlineStr">
         <is>
+          <t>Environment, Tools &amp; Tool Discovery</t>
+        </is>
+      </c>
+      <c r="Q171" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.1-batch04.json</t>
         </is>
       </c>
-      <c r="Q171" s="2" t="n">
+      <c r="R171" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -14438,10 +15294,15 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery</t>
+        </is>
+      </c>
+      <c r="Q172" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.1-batch05.json</t>
         </is>
       </c>
-      <c r="Q172" s="2" t="n">
+      <c r="R172" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14520,10 +15381,15 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
+          <t>Environment, Tools &amp; Tool Discovery, Guardrails</t>
+        </is>
+      </c>
+      <c r="Q173" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.1-batch05.json</t>
         </is>
       </c>
-      <c r="Q173" s="2" t="n">
+      <c r="R173" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14600,10 +15466,15 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
+          <t>Environment, Tools &amp; Tool Discovery</t>
+        </is>
+      </c>
+      <c r="Q174" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.1-batch05.json</t>
         </is>
       </c>
-      <c r="Q174" s="2" t="n">
+      <c r="R174" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -14682,10 +15553,15 @@
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
+          <t>Environment, Tools &amp; Tool Discovery, Guardrails</t>
+        </is>
+      </c>
+      <c r="Q175" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.1-batch06.json</t>
         </is>
       </c>
-      <c r="Q175" s="2" t="n">
+      <c r="R175" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14764,10 +15640,15 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
+          <t>Environment, Tools &amp; Tool Discovery</t>
+        </is>
+      </c>
+      <c r="Q176" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.1-batch06.json</t>
         </is>
       </c>
-      <c r="Q176" s="2" t="n">
+      <c r="R176" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -14846,10 +15727,15 @@
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
+          <t>Environment, Tools &amp; Tool Discovery, Guardrails</t>
+        </is>
+      </c>
+      <c r="Q177" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.1-batch06.json</t>
         </is>
       </c>
-      <c r="Q177" s="2" t="n">
+      <c r="R177" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -14927,10 +15813,15 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery, Guardrails</t>
+        </is>
+      </c>
+      <c r="Q178" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.1-batch07.json</t>
         </is>
       </c>
-      <c r="Q178" s="2" t="n">
+      <c r="R178" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15009,10 +15900,15 @@
       </c>
       <c r="P179" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery</t>
+        </is>
+      </c>
+      <c r="Q179" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.1-batch07.json</t>
         </is>
       </c>
-      <c r="Q179" s="2" t="n">
+      <c r="R179" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -15091,10 +15987,15 @@
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
+          <t>Environment, Tools &amp; Tool Discovery</t>
+        </is>
+      </c>
+      <c r="Q180" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.1-batch07.json</t>
         </is>
       </c>
-      <c r="Q180" s="2" t="n">
+      <c r="R180" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -15173,10 +16074,15 @@
       </c>
       <c r="P181" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery</t>
+        </is>
+      </c>
+      <c r="Q181" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.1-batch08.json</t>
         </is>
       </c>
-      <c r="Q181" s="2" t="n">
+      <c r="R181" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15255,10 +16161,15 @@
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
+          <t>Environment, Tools &amp; Tool Discovery</t>
+        </is>
+      </c>
+      <c r="Q182" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.1-batch08.json</t>
         </is>
       </c>
-      <c r="Q182" s="2" t="n">
+      <c r="R182" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -15337,10 +16248,15 @@
       </c>
       <c r="P183" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery, Guardrails</t>
+        </is>
+      </c>
+      <c r="Q183" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.1-batch08.json</t>
         </is>
       </c>
-      <c r="Q183" s="2" t="n">
+      <c r="R183" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -15419,10 +16335,15 @@
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
+          <t>Environment, Tools &amp; Tool Discovery</t>
+        </is>
+      </c>
+      <c r="Q184" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.1-batch08.json</t>
         </is>
       </c>
-      <c r="Q184" s="2" t="n">
+      <c r="R184" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -15501,10 +16422,15 @@
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
+          <t>Environment, Tools &amp; Tool Discovery</t>
+        </is>
+      </c>
+      <c r="Q185" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.1-batch08.json</t>
         </is>
       </c>
-      <c r="Q185" s="2" t="n">
+      <c r="R185" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -15581,10 +16507,15 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
+          <t>Environment, Tools &amp; Tool Discovery</t>
+        </is>
+      </c>
+      <c r="Q186" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.1-batch08.json</t>
         </is>
       </c>
-      <c r="Q186" s="2" t="n">
+      <c r="R186" s="2" t="n">
         <v>5</v>
       </c>
     </row>
@@ -15663,10 +16594,15 @@
       </c>
       <c r="P187" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery, Guardrails</t>
+        </is>
+      </c>
+      <c r="Q187" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.1-batch08.json</t>
         </is>
       </c>
-      <c r="Q187" s="2" t="n">
+      <c r="R187" s="2" t="n">
         <v>6</v>
       </c>
     </row>
@@ -15745,10 +16681,15 @@
       </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q188" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.2-batch01.json</t>
         </is>
       </c>
-      <c r="Q188" s="2" t="n">
+      <c r="R188" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15827,10 +16768,15 @@
       </c>
       <c r="P189" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery</t>
+        </is>
+      </c>
+      <c r="Q189" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.2-batch01.json</t>
         </is>
       </c>
-      <c r="Q189" s="2" t="n">
+      <c r="R189" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -15909,10 +16855,15 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
+          <t>State / State Management, Tools &amp; Tool Discovery, Orchestration</t>
+        </is>
+      </c>
+      <c r="Q190" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.2-batch01.json</t>
         </is>
       </c>
-      <c r="Q190" s="2" t="n">
+      <c r="R190" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -15991,10 +16942,15 @@
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q191" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.2-batch02.json</t>
         </is>
       </c>
-      <c r="Q191" s="2" t="n">
+      <c r="R191" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16073,10 +17029,15 @@
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
+          <t>State / State Management, Tools &amp; Tool Discovery, Orchestration</t>
+        </is>
+      </c>
+      <c r="Q192" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.2-batch02.json</t>
         </is>
       </c>
-      <c r="Q192" s="2" t="n">
+      <c r="R192" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -16155,10 +17116,15 @@
       </c>
       <c r="P193" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery</t>
+        </is>
+      </c>
+      <c r="Q193" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.2-batch02.json</t>
         </is>
       </c>
-      <c r="Q193" s="2" t="n">
+      <c r="R193" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -16235,10 +17201,15 @@
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery</t>
+        </is>
+      </c>
+      <c r="Q194" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.2-batch03.json</t>
         </is>
       </c>
-      <c r="Q194" s="2" t="n">
+      <c r="R194" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16310,10 +17281,15 @@
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
+          <t>State / State Management, Tools &amp; Tool Discovery, Orchestration</t>
+        </is>
+      </c>
+      <c r="Q195" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.2-batch03.json</t>
         </is>
       </c>
-      <c r="Q195" s="2" t="n">
+      <c r="R195" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -16392,10 +17368,15 @@
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
+          <t>State / State Management, Tools &amp; Tool Discovery, Orchestration</t>
+        </is>
+      </c>
+      <c r="Q196" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.2-batch03.json</t>
         </is>
       </c>
-      <c r="Q196" s="2" t="n">
+      <c r="R196" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -16474,10 +17455,15 @@
       </c>
       <c r="P197" s="2" t="inlineStr">
         <is>
+          <t>State / State Management, Tools &amp; Tool Discovery, Orchestration</t>
+        </is>
+      </c>
+      <c r="Q197" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.2-batch04.json</t>
         </is>
       </c>
-      <c r="Q197" s="2" t="n">
+      <c r="R197" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16556,10 +17542,15 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery</t>
+        </is>
+      </c>
+      <c r="Q198" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.2-batch04.json</t>
         </is>
       </c>
-      <c r="Q198" s="2" t="n">
+      <c r="R198" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -16638,10 +17629,15 @@
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q199" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.2-batch04.json</t>
         </is>
       </c>
-      <c r="Q199" s="2" t="n">
+      <c r="R199" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -16720,10 +17716,15 @@
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q200" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.2-batch05.json</t>
         </is>
       </c>
-      <c r="Q200" s="2" t="n">
+      <c r="R200" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16802,10 +17803,15 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery</t>
+        </is>
+      </c>
+      <c r="Q201" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.2-batch05.json</t>
         </is>
       </c>
-      <c r="Q201" s="2" t="n">
+      <c r="R201" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -16884,10 +17890,15 @@
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
+          <t>State / State Management, Tools &amp; Tool Discovery, Orchestration</t>
+        </is>
+      </c>
+      <c r="Q202" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.2-batch05.json</t>
         </is>
       </c>
-      <c r="Q202" s="2" t="n">
+      <c r="R202" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -16965,10 +17976,15 @@
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q203" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.2-batch06.json</t>
         </is>
       </c>
-      <c r="Q203" s="2" t="n">
+      <c r="R203" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17047,10 +18063,15 @@
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q204" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.2-batch06.json</t>
         </is>
       </c>
-      <c r="Q204" s="2" t="n">
+      <c r="R204" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -17129,10 +18150,15 @@
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery</t>
+        </is>
+      </c>
+      <c r="Q205" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.2-batch06.json</t>
         </is>
       </c>
-      <c r="Q205" s="2" t="n">
+      <c r="R205" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -17211,10 +18237,15 @@
       </c>
       <c r="P206" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery</t>
+        </is>
+      </c>
+      <c r="Q206" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.2-batch07.json</t>
         </is>
       </c>
-      <c r="Q206" s="2" t="n">
+      <c r="R206" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17293,10 +18324,15 @@
       </c>
       <c r="P207" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery</t>
+        </is>
+      </c>
+      <c r="Q207" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.2-batch07.json</t>
         </is>
       </c>
-      <c r="Q207" s="2" t="n">
+      <c r="R207" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -17375,10 +18411,15 @@
       </c>
       <c r="P208" s="2" t="inlineStr">
         <is>
+          <t>State / State Management, Tools &amp; Tool Discovery, Orchestration</t>
+        </is>
+      </c>
+      <c r="Q208" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.2-batch07.json</t>
         </is>
       </c>
-      <c r="Q208" s="2" t="n">
+      <c r="R208" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -17455,10 +18496,15 @@
       </c>
       <c r="P209" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery</t>
+        </is>
+      </c>
+      <c r="Q209" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.2-batch07.json</t>
         </is>
       </c>
-      <c r="Q209" s="2" t="n">
+      <c r="R209" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -17537,10 +18583,15 @@
       </c>
       <c r="P210" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q210" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.2-batch07.json</t>
         </is>
       </c>
-      <c r="Q210" s="2" t="n">
+      <c r="R210" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -17619,10 +18670,15 @@
       </c>
       <c r="P211" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery</t>
+        </is>
+      </c>
+      <c r="Q211" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.2-batch07.json</t>
         </is>
       </c>
-      <c r="Q211" s="2" t="n">
+      <c r="R211" s="2" t="n">
         <v>5</v>
       </c>
     </row>
@@ -17701,10 +18757,15 @@
       </c>
       <c r="P212" s="2" t="inlineStr">
         <is>
+          <t>State / State Management, Tools &amp; Tool Discovery, Orchestration</t>
+        </is>
+      </c>
+      <c r="Q212" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.2-batch07.json</t>
         </is>
       </c>
-      <c r="Q212" s="2" t="n">
+      <c r="R212" s="2" t="n">
         <v>6</v>
       </c>
     </row>
@@ -17783,10 +18844,15 @@
       </c>
       <c r="P213" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q213" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.2-batch07.json</t>
         </is>
       </c>
-      <c r="Q213" s="2" t="n">
+      <c r="R213" s="2" t="n">
         <v>7</v>
       </c>
     </row>
@@ -17865,10 +18931,15 @@
       </c>
       <c r="P214" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery</t>
+        </is>
+      </c>
+      <c r="Q214" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.2-batch08.json</t>
         </is>
       </c>
-      <c r="Q214" s="2" t="n">
+      <c r="R214" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17947,10 +19018,15 @@
       </c>
       <c r="P215" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery, Error Recovery, Evaluation &amp; Learning Loops</t>
+        </is>
+      </c>
+      <c r="Q215" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.3-batch01.json</t>
         </is>
       </c>
-      <c r="Q215" s="2" t="n">
+      <c r="R215" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18029,10 +19105,15 @@
       </c>
       <c r="P216" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery, Error Recovery</t>
+        </is>
+      </c>
+      <c r="Q216" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.3-batch01.json</t>
         </is>
       </c>
-      <c r="Q216" s="2" t="n">
+      <c r="R216" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -18111,10 +19192,15 @@
       </c>
       <c r="P217" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery, Error Recovery</t>
+        </is>
+      </c>
+      <c r="Q217" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.3-batch01.json</t>
         </is>
       </c>
-      <c r="Q217" s="2" t="n">
+      <c r="R217" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -18193,10 +19279,15 @@
       </c>
       <c r="P218" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery, Error Recovery, Evaluation &amp; Learning Loops</t>
+        </is>
+      </c>
+      <c r="Q218" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.3-batch02.json</t>
         </is>
       </c>
-      <c r="Q218" s="2" t="n">
+      <c r="R218" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18275,10 +19366,15 @@
       </c>
       <c r="P219" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery, Error Recovery</t>
+        </is>
+      </c>
+      <c r="Q219" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.3-batch02.json</t>
         </is>
       </c>
-      <c r="Q219" s="2" t="n">
+      <c r="R219" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -18357,10 +19453,15 @@
       </c>
       <c r="P220" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery, Error Recovery</t>
+        </is>
+      </c>
+      <c r="Q220" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.3-batch02.json</t>
         </is>
       </c>
-      <c r="Q220" s="2" t="n">
+      <c r="R220" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -18437,10 +19538,15 @@
       </c>
       <c r="P221" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery, Error Recovery</t>
+        </is>
+      </c>
+      <c r="Q221" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.3-batch03.json</t>
         </is>
       </c>
-      <c r="Q221" s="2" t="n">
+      <c r="R221" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18512,10 +19618,15 @@
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery, Error Recovery</t>
+        </is>
+      </c>
+      <c r="Q222" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.3-batch03.json</t>
         </is>
       </c>
-      <c r="Q222" s="2" t="n">
+      <c r="R222" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -18594,10 +19705,15 @@
       </c>
       <c r="P223" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery, Error Recovery, Evaluation &amp; Learning Loops</t>
+        </is>
+      </c>
+      <c r="Q223" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.3-batch03.json</t>
         </is>
       </c>
-      <c r="Q223" s="2" t="n">
+      <c r="R223" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -18676,10 +19792,15 @@
       </c>
       <c r="P224" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery, Error Recovery</t>
+        </is>
+      </c>
+      <c r="Q224" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.3-batch04.json</t>
         </is>
       </c>
-      <c r="Q224" s="2" t="n">
+      <c r="R224" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18758,10 +19879,15 @@
       </c>
       <c r="P225" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery, Error Recovery</t>
+        </is>
+      </c>
+      <c r="Q225" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.3-batch04.json</t>
         </is>
       </c>
-      <c r="Q225" s="2" t="n">
+      <c r="R225" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -18840,10 +19966,15 @@
       </c>
       <c r="P226" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery, Guardrails, Error Recovery, Evaluation &amp; Learning Loops</t>
+        </is>
+      </c>
+      <c r="Q226" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.3-batch04.json</t>
         </is>
       </c>
-      <c r="Q226" s="2" t="n">
+      <c r="R226" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -18922,10 +20053,15 @@
       </c>
       <c r="P227" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery, Error Recovery</t>
+        </is>
+      </c>
+      <c r="Q227" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.3-batch05.json</t>
         </is>
       </c>
-      <c r="Q227" s="2" t="n">
+      <c r="R227" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19004,10 +20140,15 @@
       </c>
       <c r="P228" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery, Error Recovery, Evaluation &amp; Learning Loops</t>
+        </is>
+      </c>
+      <c r="Q228" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.3-batch05.json</t>
         </is>
       </c>
-      <c r="Q228" s="2" t="n">
+      <c r="R228" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -19086,10 +20227,15 @@
       </c>
       <c r="P229" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery, Error Recovery</t>
+        </is>
+      </c>
+      <c r="Q229" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.3-batch05.json</t>
         </is>
       </c>
-      <c r="Q229" s="2" t="n">
+      <c r="R229" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -19167,10 +20313,15 @@
       </c>
       <c r="P230" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery, Error Recovery</t>
+        </is>
+      </c>
+      <c r="Q230" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.3-batch06.json</t>
         </is>
       </c>
-      <c r="Q230" s="2" t="n">
+      <c r="R230" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19249,10 +20400,15 @@
       </c>
       <c r="P231" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery, Error Recovery, Evaluation &amp; Learning Loops</t>
+        </is>
+      </c>
+      <c r="Q231" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.3-batch06.json</t>
         </is>
       </c>
-      <c r="Q231" s="2" t="n">
+      <c r="R231" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -19331,10 +20487,15 @@
       </c>
       <c r="P232" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery, Error Recovery</t>
+        </is>
+      </c>
+      <c r="Q232" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.3-batch06.json</t>
         </is>
       </c>
-      <c r="Q232" s="2" t="n">
+      <c r="R232" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -19413,10 +20574,15 @@
       </c>
       <c r="P233" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery, Error Recovery</t>
+        </is>
+      </c>
+      <c r="Q233" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.3-batch07.json</t>
         </is>
       </c>
-      <c r="Q233" s="2" t="n">
+      <c r="R233" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19495,10 +20661,15 @@
       </c>
       <c r="P234" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery, Guardrails, Error Recovery, Evaluation &amp; Learning Loops</t>
+        </is>
+      </c>
+      <c r="Q234" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.3-batch07.json</t>
         </is>
       </c>
-      <c r="Q234" s="2" t="n">
+      <c r="R234" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -19577,10 +20748,15 @@
       </c>
       <c r="P235" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery, Error Recovery</t>
+        </is>
+      </c>
+      <c r="Q235" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.3-batch07.json</t>
         </is>
       </c>
-      <c r="Q235" s="2" t="n">
+      <c r="R235" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -19659,10 +20835,15 @@
       </c>
       <c r="P236" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery, Error Recovery, Evaluation &amp; Learning Loops</t>
+        </is>
+      </c>
+      <c r="Q236" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.3-batch07.json</t>
         </is>
       </c>
-      <c r="Q236" s="2" t="n">
+      <c r="R236" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -19741,10 +20922,15 @@
       </c>
       <c r="P237" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery, Error Recovery</t>
+        </is>
+      </c>
+      <c r="Q237" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.3-batch07.json</t>
         </is>
       </c>
-      <c r="Q237" s="2" t="n">
+      <c r="R237" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -19822,10 +21008,15 @@
       </c>
       <c r="P238" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery, Error Recovery, Evaluation &amp; Learning Loops</t>
+        </is>
+      </c>
+      <c r="Q238" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.3-batch07.json</t>
         </is>
       </c>
-      <c r="Q238" s="2" t="n">
+      <c r="R238" s="2" t="n">
         <v>5</v>
       </c>
     </row>
@@ -19904,10 +21095,15 @@
       </c>
       <c r="P239" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery, Error Recovery</t>
+        </is>
+      </c>
+      <c r="Q239" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.3-batch07.json</t>
         </is>
       </c>
-      <c r="Q239" s="2" t="n">
+      <c r="R239" s="2" t="n">
         <v>6</v>
       </c>
     </row>
@@ -19986,10 +21182,15 @@
       </c>
       <c r="P240" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery, Error Recovery</t>
+        </is>
+      </c>
+      <c r="Q240" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.3-batch07.json</t>
         </is>
       </c>
-      <c r="Q240" s="2" t="n">
+      <c r="R240" s="2" t="n">
         <v>7</v>
       </c>
     </row>
@@ -20068,10 +21269,15 @@
       </c>
       <c r="P241" s="2" t="inlineStr">
         <is>
+          <t>Tools &amp; Tool Discovery, Error Recovery, Evaluation &amp; Learning Loops</t>
+        </is>
+      </c>
+      <c r="Q241" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d3\3.3-batch07.json</t>
         </is>
       </c>
-      <c r="Q241" s="2" t="n">
+      <c r="R241" s="2" t="n">
         <v>8</v>
       </c>
     </row>
@@ -20150,10 +21356,15 @@
       </c>
       <c r="P242" s="2" t="inlineStr">
         <is>
+          <t>State / State Management, Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q242" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.1-batch01.json</t>
         </is>
       </c>
-      <c r="Q242" s="2" t="n">
+      <c r="R242" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -20232,10 +21443,15 @@
       </c>
       <c r="P243" s="2" t="inlineStr">
         <is>
+          <t>State / State Management, Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q243" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.1-batch01.json</t>
         </is>
       </c>
-      <c r="Q243" s="2" t="n">
+      <c r="R243" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -20314,10 +21530,15 @@
       </c>
       <c r="P244" s="2" t="inlineStr">
         <is>
+          <t>State / State Management, Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q244" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.1-batch01.json</t>
         </is>
       </c>
-      <c r="Q244" s="2" t="n">
+      <c r="R244" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -20396,10 +21617,15 @@
       </c>
       <c r="P245" s="2" t="inlineStr">
         <is>
+          <t>State / State Management, Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q245" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.1-batch02.json</t>
         </is>
       </c>
-      <c r="Q245" s="2" t="n">
+      <c r="R245" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -20478,10 +21704,15 @@
       </c>
       <c r="P246" s="2" t="inlineStr">
         <is>
+          <t>State / State Management, Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q246" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.1-batch02.json</t>
         </is>
       </c>
-      <c r="Q246" s="2" t="n">
+      <c r="R246" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -20560,10 +21791,15 @@
       </c>
       <c r="P247" s="2" t="inlineStr">
         <is>
+          <t>State / State Management, Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q247" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.1-batch02.json</t>
         </is>
       </c>
-      <c r="Q247" s="2" t="n">
+      <c r="R247" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -20641,10 +21877,15 @@
       </c>
       <c r="P248" s="2" t="inlineStr">
         <is>
+          <t>State / State Management, Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q248" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.1-batch03.json</t>
         </is>
       </c>
-      <c r="Q248" s="2" t="n">
+      <c r="R248" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -20716,10 +21957,15 @@
       </c>
       <c r="P249" s="2" t="inlineStr">
         <is>
+          <t>State / State Management, Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q249" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.1-batch03.json</t>
         </is>
       </c>
-      <c r="Q249" s="2" t="n">
+      <c r="R249" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -20798,10 +22044,15 @@
       </c>
       <c r="P250" s="2" t="inlineStr">
         <is>
+          <t>State / State Management, Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q250" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.1-batch03.json</t>
         </is>
       </c>
-      <c r="Q250" s="2" t="n">
+      <c r="R250" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -20880,10 +22131,15 @@
       </c>
       <c r="P251" s="2" t="inlineStr">
         <is>
+          <t>State / State Management, Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q251" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.1-batch04.json</t>
         </is>
       </c>
-      <c r="Q251" s="2" t="n">
+      <c r="R251" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -20962,10 +22218,15 @@
       </c>
       <c r="P252" s="2" t="inlineStr">
         <is>
+          <t>State / State Management, Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q252" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.1-batch04.json</t>
         </is>
       </c>
-      <c r="Q252" s="2" t="n">
+      <c r="R252" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -21044,10 +22305,15 @@
       </c>
       <c r="P253" s="2" t="inlineStr">
         <is>
+          <t>State / State Management, Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q253" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.1-batch04.json</t>
         </is>
       </c>
-      <c r="Q253" s="2" t="n">
+      <c r="R253" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -21126,10 +22392,15 @@
       </c>
       <c r="P254" s="2" t="inlineStr">
         <is>
+          <t>State / State Management, Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q254" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.1-batch05.json</t>
         </is>
       </c>
-      <c r="Q254" s="2" t="n">
+      <c r="R254" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21208,10 +22479,15 @@
       </c>
       <c r="P255" s="2" t="inlineStr">
         <is>
+          <t>State / State Management, Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q255" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.1-batch05.json</t>
         </is>
       </c>
-      <c r="Q255" s="2" t="n">
+      <c r="R255" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -21290,10 +22566,15 @@
       </c>
       <c r="P256" s="2" t="inlineStr">
         <is>
+          <t>State / State Management, Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q256" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.1-batch05.json</t>
         </is>
       </c>
-      <c r="Q256" s="2" t="n">
+      <c r="R256" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -21371,10 +22652,15 @@
       </c>
       <c r="P257" s="2" t="inlineStr">
         <is>
+          <t>State / State Management, Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q257" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.1-batch06.json</t>
         </is>
       </c>
-      <c r="Q257" s="2" t="n">
+      <c r="R257" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21453,10 +22739,15 @@
       </c>
       <c r="P258" s="2" t="inlineStr">
         <is>
+          <t>State / State Management, Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q258" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.1-batch06.json</t>
         </is>
       </c>
-      <c r="Q258" s="2" t="n">
+      <c r="R258" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -21535,10 +22826,15 @@
       </c>
       <c r="P259" s="2" t="inlineStr">
         <is>
+          <t>State / State Management, Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q259" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.1-batch06.json</t>
         </is>
       </c>
-      <c r="Q259" s="2" t="n">
+      <c r="R259" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -21617,10 +22913,15 @@
       </c>
       <c r="P260" s="2" t="inlineStr">
         <is>
+          <t>State / State Management, Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q260" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.1-batch07.json</t>
         </is>
       </c>
-      <c r="Q260" s="2" t="n">
+      <c r="R260" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21699,10 +23000,15 @@
       </c>
       <c r="P261" s="2" t="inlineStr">
         <is>
+          <t>State / State Management, Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q261" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.1-batch07.json</t>
         </is>
       </c>
-      <c r="Q261" s="2" t="n">
+      <c r="R261" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -21781,10 +23087,15 @@
       </c>
       <c r="P262" s="2" t="inlineStr">
         <is>
+          <t>State / State Management, Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q262" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.1-batch07.json</t>
         </is>
       </c>
-      <c r="Q262" s="2" t="n">
+      <c r="R262" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -21863,10 +23174,15 @@
       </c>
       <c r="P263" s="2" t="inlineStr">
         <is>
+          <t>State / State Management, Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q263" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.1-batch07.json</t>
         </is>
       </c>
-      <c r="Q263" s="2" t="n">
+      <c r="R263" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -21945,10 +23261,15 @@
       </c>
       <c r="P264" s="2" t="inlineStr">
         <is>
+          <t>State / State Management, Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q264" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.1-batch07.json</t>
         </is>
       </c>
-      <c r="Q264" s="2" t="n">
+      <c r="R264" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -22026,10 +23347,15 @@
       </c>
       <c r="P265" s="2" t="inlineStr">
         <is>
+          <t>State / State Management, Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q265" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.1-batch07.json</t>
         </is>
       </c>
-      <c r="Q265" s="2" t="n">
+      <c r="R265" s="2" t="n">
         <v>5</v>
       </c>
     </row>
@@ -22108,10 +23434,15 @@
       </c>
       <c r="P266" s="2" t="inlineStr">
         <is>
+          <t>State / State Management, Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q266" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.1-batch07.json</t>
         </is>
       </c>
-      <c r="Q266" s="2" t="n">
+      <c r="R266" s="2" t="n">
         <v>6</v>
       </c>
     </row>
@@ -22190,10 +23521,15 @@
       </c>
       <c r="P267" s="2" t="inlineStr">
         <is>
+          <t>State / State Management, Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q267" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.1-batch07.json</t>
         </is>
       </c>
-      <c r="Q267" s="2" t="n">
+      <c r="R267" s="2" t="n">
         <v>7</v>
       </c>
     </row>
@@ -22272,10 +23608,15 @@
       </c>
       <c r="P268" s="2" t="inlineStr">
         <is>
+          <t>State / State Management, Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q268" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.1-batch07.json</t>
         </is>
       </c>
-      <c r="Q268" s="2" t="n">
+      <c r="R268" s="2" t="n">
         <v>8</v>
       </c>
     </row>
@@ -22354,10 +23695,15 @@
       </c>
       <c r="P269" s="2" t="inlineStr">
         <is>
+          <t>State / State Management, Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q269" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.1-batch07.json</t>
         </is>
       </c>
-      <c r="Q269" s="2" t="n">
+      <c r="R269" s="2" t="n">
         <v>9</v>
       </c>
     </row>
@@ -22436,10 +23782,15 @@
       </c>
       <c r="P270" s="2" t="inlineStr">
         <is>
+          <t>Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q270" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.2-batch01.json</t>
         </is>
       </c>
-      <c r="Q270" s="2" t="n">
+      <c r="R270" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -22518,10 +23869,15 @@
       </c>
       <c r="P271" s="2" t="inlineStr">
         <is>
+          <t>Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q271" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.2-batch01.json</t>
         </is>
       </c>
-      <c r="Q271" s="2" t="n">
+      <c r="R271" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -22600,10 +23956,15 @@
       </c>
       <c r="P272" s="2" t="inlineStr">
         <is>
+          <t>Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q272" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.2-batch01.json</t>
         </is>
       </c>
-      <c r="Q272" s="2" t="n">
+      <c r="R272" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -22682,10 +24043,15 @@
       </c>
       <c r="P273" s="2" t="inlineStr">
         <is>
+          <t>Memory</t>
+        </is>
+      </c>
+      <c r="Q273" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.2-batch02.json</t>
         </is>
       </c>
-      <c r="Q273" s="2" t="n">
+      <c r="R273" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -22764,10 +24130,15 @@
       </c>
       <c r="P274" s="2" t="inlineStr">
         <is>
+          <t>Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q274" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.2-batch02.json</t>
         </is>
       </c>
-      <c r="Q274" s="2" t="n">
+      <c r="R274" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -22846,10 +24217,15 @@
       </c>
       <c r="P275" s="2" t="inlineStr">
         <is>
+          <t>Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q275" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.2-batch02.json</t>
         </is>
       </c>
-      <c r="Q275" s="2" t="n">
+      <c r="R275" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -22926,10 +24302,15 @@
       </c>
       <c r="P276" s="2" t="inlineStr">
         <is>
+          <t>Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q276" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.2-batch03.json</t>
         </is>
       </c>
-      <c r="Q276" s="2" t="n">
+      <c r="R276" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -23001,10 +24382,15 @@
       </c>
       <c r="P277" s="2" t="inlineStr">
         <is>
+          <t>Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q277" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.2-batch03.json</t>
         </is>
       </c>
-      <c r="Q277" s="2" t="n">
+      <c r="R277" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -23083,10 +24469,15 @@
       </c>
       <c r="P278" s="2" t="inlineStr">
         <is>
+          <t>Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q278" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.2-batch03.json</t>
         </is>
       </c>
-      <c r="Q278" s="2" t="n">
+      <c r="R278" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -23165,10 +24556,15 @@
       </c>
       <c r="P279" s="2" t="inlineStr">
         <is>
+          <t>Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q279" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.2-batch04.json</t>
         </is>
       </c>
-      <c r="Q279" s="2" t="n">
+      <c r="R279" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -23247,10 +24643,15 @@
       </c>
       <c r="P280" s="2" t="inlineStr">
         <is>
+          <t>Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q280" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.2-batch04.json</t>
         </is>
       </c>
-      <c r="Q280" s="2" t="n">
+      <c r="R280" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -23329,10 +24730,15 @@
       </c>
       <c r="P281" s="2" t="inlineStr">
         <is>
+          <t>Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q281" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.2-batch04.json</t>
         </is>
       </c>
-      <c r="Q281" s="2" t="n">
+      <c r="R281" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -23411,10 +24817,15 @@
       </c>
       <c r="P282" s="2" t="inlineStr">
         <is>
+          <t>Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q282" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.2-batch05.json</t>
         </is>
       </c>
-      <c r="Q282" s="2" t="n">
+      <c r="R282" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -23493,10 +24904,15 @@
       </c>
       <c r="P283" s="2" t="inlineStr">
         <is>
+          <t>Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q283" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.2-batch05.json</t>
         </is>
       </c>
-      <c r="Q283" s="2" t="n">
+      <c r="R283" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -23575,10 +24991,15 @@
       </c>
       <c r="P284" s="2" t="inlineStr">
         <is>
+          <t>Memory</t>
+        </is>
+      </c>
+      <c r="Q284" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.2-batch05.json</t>
         </is>
       </c>
-      <c r="Q284" s="2" t="n">
+      <c r="R284" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -23656,10 +25077,15 @@
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
+          <t>Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q285" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.2-batch06.json</t>
         </is>
       </c>
-      <c r="Q285" s="2" t="n">
+      <c r="R285" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -23738,10 +25164,15 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
+          <t>Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q286" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.2-batch06.json</t>
         </is>
       </c>
-      <c r="Q286" s="2" t="n">
+      <c r="R286" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -23820,10 +25251,15 @@
       </c>
       <c r="P287" s="2" t="inlineStr">
         <is>
+          <t>Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q287" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.2-batch07.json</t>
         </is>
       </c>
-      <c r="Q287" s="2" t="n">
+      <c r="R287" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -23902,10 +25338,15 @@
       </c>
       <c r="P288" s="2" t="inlineStr">
         <is>
+          <t>Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q288" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.2-batch07.json</t>
         </is>
       </c>
-      <c r="Q288" s="2" t="n">
+      <c r="R288" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -23984,10 +25425,15 @@
       </c>
       <c r="P289" s="2" t="inlineStr">
         <is>
+          <t>Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q289" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.2-batch07.json</t>
         </is>
       </c>
-      <c r="Q289" s="2" t="n">
+      <c r="R289" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -24066,10 +25512,15 @@
       </c>
       <c r="P290" s="2" t="inlineStr">
         <is>
+          <t>Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q290" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.2-batch07.json</t>
         </is>
       </c>
-      <c r="Q290" s="2" t="n">
+      <c r="R290" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -24148,10 +25599,15 @@
       </c>
       <c r="P291" s="2" t="inlineStr">
         <is>
+          <t>Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q291" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.2-batch07.json</t>
         </is>
       </c>
-      <c r="Q291" s="2" t="n">
+      <c r="R291" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -24230,10 +25686,15 @@
       </c>
       <c r="P292" s="2" t="inlineStr">
         <is>
+          <t>Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q292" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.2-batch07.json</t>
         </is>
       </c>
-      <c r="Q292" s="2" t="n">
+      <c r="R292" s="2" t="n">
         <v>5</v>
       </c>
     </row>
@@ -24312,10 +25773,15 @@
       </c>
       <c r="P293" s="2" t="inlineStr">
         <is>
+          <t>Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q293" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.2-batch07.json</t>
         </is>
       </c>
-      <c r="Q293" s="2" t="n">
+      <c r="R293" s="2" t="n">
         <v>6</v>
       </c>
     </row>
@@ -24394,10 +25860,15 @@
       </c>
       <c r="P294" s="2" t="inlineStr">
         <is>
+          <t>Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q294" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.2-batch07.json</t>
         </is>
       </c>
-      <c r="Q294" s="2" t="n">
+      <c r="R294" s="2" t="n">
         <v>7</v>
       </c>
     </row>
@@ -24476,10 +25947,15 @@
       </c>
       <c r="P295" s="2" t="inlineStr">
         <is>
+          <t>Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q295" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.2-batch07.json</t>
         </is>
       </c>
-      <c r="Q295" s="2" t="n">
+      <c r="R295" s="2" t="n">
         <v>8</v>
       </c>
     </row>
@@ -24558,10 +26034,15 @@
       </c>
       <c r="P296" s="2" t="inlineStr">
         <is>
+          <t>Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q296" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.3-batch01.json</t>
         </is>
       </c>
-      <c r="Q296" s="2" t="n">
+      <c r="R296" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -24640,10 +26121,15 @@
       </c>
       <c r="P297" s="2" t="inlineStr">
         <is>
+          <t>Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q297" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.3-batch01.json</t>
         </is>
       </c>
-      <c r="Q297" s="2" t="n">
+      <c r="R297" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -24722,10 +26208,15 @@
       </c>
       <c r="P298" s="2" t="inlineStr">
         <is>
+          <t>Memory, Context Engineering, Evaluation &amp; Learning Loops</t>
+        </is>
+      </c>
+      <c r="Q298" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.3-batch01.json</t>
         </is>
       </c>
-      <c r="Q298" s="2" t="n">
+      <c r="R298" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -24804,10 +26295,15 @@
       </c>
       <c r="P299" s="2" t="inlineStr">
         <is>
+          <t>Memory, Context Engineering, Evaluation &amp; Learning Loops</t>
+        </is>
+      </c>
+      <c r="Q299" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.3-batch02.json</t>
         </is>
       </c>
-      <c r="Q299" s="2" t="n">
+      <c r="R299" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -24886,10 +26382,15 @@
       </c>
       <c r="P300" s="2" t="inlineStr">
         <is>
+          <t>Memory, Context Engineering, Guardrails, Evaluation &amp; Learning Loops</t>
+        </is>
+      </c>
+      <c r="Q300" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.3-batch02.json</t>
         </is>
       </c>
-      <c r="Q300" s="2" t="n">
+      <c r="R300" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -24968,10 +26469,15 @@
       </c>
       <c r="P301" s="2" t="inlineStr">
         <is>
+          <t>Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q301" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.3-batch02.json</t>
         </is>
       </c>
-      <c r="Q301" s="2" t="n">
+      <c r="R301" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -25048,10 +26554,15 @@
       </c>
       <c r="P302" s="2" t="inlineStr">
         <is>
+          <t>Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q302" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.3-batch03.json</t>
         </is>
       </c>
-      <c r="Q302" s="2" t="n">
+      <c r="R302" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -25123,10 +26634,15 @@
       </c>
       <c r="P303" s="2" t="inlineStr">
         <is>
+          <t>Memory, Context Engineering, Evaluation &amp; Learning Loops</t>
+        </is>
+      </c>
+      <c r="Q303" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.3-batch03.json</t>
         </is>
       </c>
-      <c r="Q303" s="2" t="n">
+      <c r="R303" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -25205,10 +26721,15 @@
       </c>
       <c r="P304" s="2" t="inlineStr">
         <is>
+          <t>Memory, Context Engineering, Evaluation &amp; Learning Loops</t>
+        </is>
+      </c>
+      <c r="Q304" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.3-batch03.json</t>
         </is>
       </c>
-      <c r="Q304" s="2" t="n">
+      <c r="R304" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -25287,10 +26808,15 @@
       </c>
       <c r="P305" s="2" t="inlineStr">
         <is>
+          <t>Memory, Context Engineering, Evaluation &amp; Learning Loops</t>
+        </is>
+      </c>
+      <c r="Q305" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.3-batch04.json</t>
         </is>
       </c>
-      <c r="Q305" s="2" t="n">
+      <c r="R305" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -25369,10 +26895,15 @@
       </c>
       <c r="P306" s="2" t="inlineStr">
         <is>
+          <t>Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q306" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.3-batch04.json</t>
         </is>
       </c>
-      <c r="Q306" s="2" t="n">
+      <c r="R306" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -25451,10 +26982,15 @@
       </c>
       <c r="P307" s="2" t="inlineStr">
         <is>
+          <t>Memory, Context Engineering, Evaluation &amp; Learning Loops</t>
+        </is>
+      </c>
+      <c r="Q307" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.3-batch04.json</t>
         </is>
       </c>
-      <c r="Q307" s="2" t="n">
+      <c r="R307" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -25533,10 +27069,15 @@
       </c>
       <c r="P308" s="2" t="inlineStr">
         <is>
+          <t>Memory, Context Engineering, Evaluation &amp; Learning Loops</t>
+        </is>
+      </c>
+      <c r="Q308" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.3-batch05.json</t>
         </is>
       </c>
-      <c r="Q308" s="2" t="n">
+      <c r="R308" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -25615,10 +27156,15 @@
       </c>
       <c r="P309" s="2" t="inlineStr">
         <is>
+          <t>Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q309" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.3-batch05.json</t>
         </is>
       </c>
-      <c r="Q309" s="2" t="n">
+      <c r="R309" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -25697,10 +27243,15 @@
       </c>
       <c r="P310" s="2" t="inlineStr">
         <is>
+          <t>Memory, Context Engineering, Evaluation &amp; Learning Loops</t>
+        </is>
+      </c>
+      <c r="Q310" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.3-batch05.json</t>
         </is>
       </c>
-      <c r="Q310" s="2" t="n">
+      <c r="R310" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -25777,10 +27328,15 @@
       </c>
       <c r="P311" s="2" t="inlineStr">
         <is>
+          <t>Memory, Context Engineering, Evaluation &amp; Learning Loops</t>
+        </is>
+      </c>
+      <c r="Q311" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.3-batch06.json</t>
         </is>
       </c>
-      <c r="Q311" s="2" t="n">
+      <c r="R311" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -25859,10 +27415,15 @@
       </c>
       <c r="P312" s="2" t="inlineStr">
         <is>
+          <t>Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q312" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.3-batch06.json</t>
         </is>
       </c>
-      <c r="Q312" s="2" t="n">
+      <c r="R312" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -25941,10 +27502,15 @@
       </c>
       <c r="P313" s="2" t="inlineStr">
         <is>
+          <t>Memory, Context Engineering, Evaluation &amp; Learning Loops</t>
+        </is>
+      </c>
+      <c r="Q313" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.3-batch06.json</t>
         </is>
       </c>
-      <c r="Q313" s="2" t="n">
+      <c r="R313" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -26023,10 +27589,15 @@
       </c>
       <c r="P314" s="2" t="inlineStr">
         <is>
+          <t>Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q314" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.3-batch07.json</t>
         </is>
       </c>
-      <c r="Q314" s="2" t="n">
+      <c r="R314" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -26105,10 +27676,15 @@
       </c>
       <c r="P315" s="2" t="inlineStr">
         <is>
+          <t>Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q315" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.3-batch07.json</t>
         </is>
       </c>
-      <c r="Q315" s="2" t="n">
+      <c r="R315" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -26187,10 +27763,15 @@
       </c>
       <c r="P316" s="2" t="inlineStr">
         <is>
+          <t>Memory, Context Engineering, Evaluation &amp; Learning Loops</t>
+        </is>
+      </c>
+      <c r="Q316" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.3-batch07.json</t>
         </is>
       </c>
-      <c r="Q316" s="2" t="n">
+      <c r="R316" s="2" t="n">
         <v>2</v>
       </c>
     </row>
@@ -26269,10 +27850,15 @@
       </c>
       <c r="P317" s="2" t="inlineStr">
         <is>
+          <t>Memory, Context Engineering, Evaluation &amp; Learning Loops</t>
+        </is>
+      </c>
+      <c r="Q317" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.3-batch07.json</t>
         </is>
       </c>
-      <c r="Q317" s="2" t="n">
+      <c r="R317" s="2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -26351,10 +27937,15 @@
       </c>
       <c r="P318" s="2" t="inlineStr">
         <is>
+          <t>Memory, Context Engineering, Evaluation &amp; Learning Loops</t>
+        </is>
+      </c>
+      <c r="Q318" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.3-batch07.json</t>
         </is>
       </c>
-      <c r="Q318" s="2" t="n">
+      <c r="R318" s="2" t="n">
         <v>4</v>
       </c>
     </row>
@@ -26433,10 +28024,15 @@
       </c>
       <c r="P319" s="2" t="inlineStr">
         <is>
+          <t>Memory, Context Engineering</t>
+        </is>
+      </c>
+      <c r="Q319" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.3-batch07.json</t>
         </is>
       </c>
-      <c r="Q319" s="2" t="n">
+      <c r="R319" s="2" t="n">
         <v>5</v>
       </c>
     </row>
@@ -26515,10 +28111,15 @@
       </c>
       <c r="P320" s="2" t="inlineStr">
         <is>
+          <t>Memory, Context Engineering, Evaluation &amp; Learning Loops</t>
+        </is>
+      </c>
+      <c r="Q320" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.3-batch07.json</t>
         </is>
       </c>
-      <c r="Q320" s="2" t="n">
+      <c r="R320" s="2" t="n">
         <v>6</v>
       </c>
     </row>
@@ -26597,15 +28198,20 @@
       </c>
       <c r="P321" s="2" t="inlineStr">
         <is>
+          <t>Memory, Context Engineering, Evaluation &amp; Learning Loops</t>
+        </is>
+      </c>
+      <c r="Q321" s="2" t="inlineStr">
+        <is>
           <t>data\questions\d4\4.3-batch07.json</t>
         </is>
       </c>
-      <c r="Q321" s="2" t="n">
+      <c r="R321" s="2" t="n">
         <v>7</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q321"/>
+  <autoFilter ref="A1:R321"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>